--- a/Tests/excel/module04_test_cases.xlsx
+++ b/Tests/excel/module04_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module04" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Module04" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module04'!$A$1:$N$24</definedName>
@@ -398,14 +398,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -429,10 +429,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -456,10 +456,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -483,10 +483,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -515,8 +515,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,8 +542,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -584,9 +584,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/Tests/excel/module04_test_cases.xlsx
+++ b/Tests/excel/module04_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Module04" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module04" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module04'!$A$1:$N$24</definedName>
@@ -398,14 +398,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -429,10 +429,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -456,10 +456,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -483,10 +483,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -515,8 +515,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,8 +542,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -584,9 +584,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/Tests/excel/module04_test_cases.xlsx
+++ b/Tests/excel/module04_test_cases.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module04" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module04'!$A$1:$N$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module04'!$A$1:$O$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1009,15 +1009,15 @@
         </is>
       </c>
       <c r="C9" s="24">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A9, 'Module04'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A9, 'Module04'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D9" s="25">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A9, 'Module04'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A9, 'Module04'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A9, 'Module04'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A9, 'Module04'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F9" s="27">
@@ -1037,15 +1037,15 @@
         </is>
       </c>
       <c r="C10" s="30">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A10, 'Module04'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A10, 'Module04'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D10" s="31">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A10, 'Module04'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A10, 'Module04'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E10" s="32">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A10, 'Module04'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A10, 'Module04'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F10" s="33">
@@ -1065,15 +1065,15 @@
         </is>
       </c>
       <c r="C11" s="24">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A11, 'Module04'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A11, 'Module04'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D11" s="25">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A11, 'Module04'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A11, 'Module04'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E11" s="26">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A11, 'Module04'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A11, 'Module04'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F11" s="27">
@@ -1093,15 +1093,15 @@
         </is>
       </c>
       <c r="C12" s="30">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A12, 'Module04'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A12, 'Module04'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D12" s="31">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A12, 'Module04'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A12, 'Module04'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E12" s="32">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A12, 'Module04'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A12, 'Module04'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F12" s="33">
@@ -1121,15 +1121,15 @@
         </is>
       </c>
       <c r="C13" s="24">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A13, 'Module04'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A13, 'Module04'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D13" s="25">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A13, 'Module04'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A13, 'Module04'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E13" s="26">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A13, 'Module04'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A13, 'Module04'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F13" s="27">
@@ -1149,15 +1149,15 @@
         </is>
       </c>
       <c r="C14" s="30">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A14, 'Module04'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A14, 'Module04'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D14" s="31">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A14, 'Module04'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A14, 'Module04'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E14" s="32">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A14, 'Module04'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A14, 'Module04'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F14" s="33">
@@ -1177,15 +1177,15 @@
         </is>
       </c>
       <c r="C15" s="24">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A15, 'Module04'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A15, 'Module04'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D15" s="25">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A15, 'Module04'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A15, 'Module04'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E15" s="26">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A15, 'Module04'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A15, 'Module04'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F15" s="27">
@@ -1205,15 +1205,15 @@
         </is>
       </c>
       <c r="C16" s="30">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A16, 'Module04'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A16, 'Module04'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D16" s="31">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A16, 'Module04'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A16, 'Module04'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E16" s="32">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A16, 'Module04'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A16, 'Module04'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F16" s="33">
@@ -1233,15 +1233,15 @@
         </is>
       </c>
       <c r="C17" s="24">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A17, 'Module04'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A17, 'Module04'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D17" s="25">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A17, 'Module04'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A17, 'Module04'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E17" s="26">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A17, 'Module04'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$24, A17, 'Module04'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F17" s="27">
@@ -1288,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1303,8 +1303,9 @@
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1370,10 +1371,15 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1444,12 +1450,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F01</t>
         </is>
@@ -1517,12 +1524,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr"/>
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F01, Optional Fields 6.2</t>
         </is>
@@ -1588,12 +1596,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F02, Academic Warning 6.3</t>
         </is>
@@ -1659,12 +1668,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F02, Optional Fields 6.2, Validation Rules 7</t>
         </is>
@@ -1729,12 +1739,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F03, One Record per Student per Semester 6.1</t>
         </is>
@@ -1800,12 +1811,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N7" s="9" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F04, Automatic Draft Saving 6.5</t>
         </is>
@@ -1871,12 +1883,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F05, Draft Recovery 6.6</t>
         </is>
@@ -1941,12 +1954,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F05, Draft Recovery 6.6</t>
         </is>
@@ -2012,12 +2026,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F06, Batch Feedback 6.7</t>
         </is>
@@ -2083,12 +2098,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N11" s="9" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F06, Batch Feedback 6.7</t>
         </is>
@@ -2154,12 +2170,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F07, Concurrent Editing 6.8</t>
         </is>
@@ -2225,12 +2242,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N13" s="9" t="inlineStr">
+      <c r="O13" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F07, Concurrent Editing 6.8</t>
         </is>
@@ -2295,12 +2313,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F08, PDF Export 6.9</t>
         </is>
@@ -2364,12 +2383,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: Business Rules, Trend Chart 6.10</t>
         </is>
@@ -2433,12 +2453,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M16" s="10" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: Business Rules, Trend Chart 6.10</t>
         </is>
@@ -2504,12 +2525,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N17" s="9" t="inlineStr">
+      <c r="O17" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: Business Rules, Badge Display 6.4</t>
         </is>
@@ -2575,12 +2597,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: Business Rules, Badge Display 6.4</t>
         </is>
@@ -2646,12 +2669,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N19" s="9" t="inlineStr">
+      <c r="O19" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: Validation Rules 7</t>
         </is>
@@ -2717,12 +2741,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: Validation Rules 7</t>
         </is>
@@ -2787,12 +2812,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="O21" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: General Rules, User Roles</t>
         </is>
@@ -2856,12 +2882,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: General Rules, User Roles</t>
         </is>
@@ -2926,12 +2953,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N23" s="9" t="inlineStr">
+      <c r="O23" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F04, Automatic Draft Saving 6.5, Out of Scope 12</t>
         </is>
@@ -2997,24 +3025,25 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M24" s="10" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F06</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N24"/>
+  <autoFilter ref="A1:O24"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
       <formula1>"Passed,Failed,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
+    <dataValidation sqref="N2:N124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Tests/excel/module04_test_cases.xlsx
+++ b/Tests/excel/module04_test_cases.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module04" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module04'!$A$1:$O$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module04'!$A$1:$O$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,7 +48,7 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="0064748B"/>
+      <color rgb="00137333"/>
       <sz val="10"/>
     </font>
     <font>
@@ -73,12 +73,6 @@
       <name val="Segoe UI"/>
       <i val="1"/>
       <color rgb="00555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00137333"/>
       <sz val="10"/>
     </font>
     <font>
@@ -145,8 +139,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
-        <bgColor rgb="00F1F5F9"/>
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
     <fill>
@@ -175,8 +169,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
-        <bgColor rgb="00E6F4EA"/>
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -254,25 +248,25 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -291,7 +285,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,16 +303,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1009,15 +1003,15 @@
         </is>
       </c>
       <c r="C9" s="24">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A9, 'Module04'!$N$2:$N$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A9, 'Module04'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D9" s="25">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A9, 'Module04'!$N$2:$N$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A9, 'Module04'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A9, 'Module04'!$N$2:$N$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A9, 'Module04'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F9" s="27">
@@ -1037,15 +1031,15 @@
         </is>
       </c>
       <c r="C10" s="30">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A10, 'Module04'!$N$2:$N$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A10, 'Module04'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D10" s="31">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A10, 'Module04'!$N$2:$N$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A10, 'Module04'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E10" s="32">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A10, 'Module04'!$N$2:$N$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A10, 'Module04'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F10" s="33">
@@ -1056,24 +1050,24 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>M04-F03</t>
+          <t>M04-F04</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>Duplicate Record Prevention</t>
+          <t>Auto Draft Saving</t>
         </is>
       </c>
       <c r="C11" s="24">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A11, 'Module04'!$N$2:$N$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A11, 'Module04'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D11" s="25">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A11, 'Module04'!$N$2:$N$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A11, 'Module04'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E11" s="26">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A11, 'Module04'!$N$2:$N$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A11, 'Module04'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F11" s="27">
@@ -1084,24 +1078,24 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="28" t="inlineStr">
         <is>
-          <t>M04-F04</t>
+          <t>M04-F05</t>
         </is>
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Auto Draft Saving</t>
+          <t>Draft Recovery / Discard</t>
         </is>
       </c>
       <c r="C12" s="30">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A12, 'Module04'!$N$2:$N$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A12, 'Module04'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D12" s="31">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A12, 'Module04'!$N$2:$N$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A12, 'Module04'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E12" s="32">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A12, 'Module04'!$N$2:$N$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A12, 'Module04'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F12" s="33">
@@ -1112,24 +1106,24 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>M04-F05</t>
+          <t>M04-F06</t>
         </is>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Draft Recovery / Discard</t>
+          <t>Batch Feedback Entry</t>
         </is>
       </c>
       <c r="C13" s="24">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A13, 'Module04'!$N$2:$N$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A13, 'Module04'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D13" s="25">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A13, 'Module04'!$N$2:$N$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A13, 'Module04'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E13" s="26">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A13, 'Module04'!$N$2:$N$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A13, 'Module04'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F13" s="27">
@@ -1140,24 +1134,24 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="28" t="inlineStr">
         <is>
-          <t>M04-F06</t>
+          <t>M04-F07</t>
         </is>
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>Batch Feedback Entry</t>
+          <t>Concurrent Edit Conflict Handling</t>
         </is>
       </c>
       <c r="C14" s="30">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A14, 'Module04'!$N$2:$N$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A14, 'Module04'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D14" s="31">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A14, 'Module04'!$N$2:$N$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A14, 'Module04'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E14" s="32">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A14, 'Module04'!$N$2:$N$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A14, 'Module04'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F14" s="33">
@@ -1168,24 +1162,24 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>M04-F07</t>
+          <t>M04-F08</t>
         </is>
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>Concurrent Edit Conflict Handling</t>
+          <t>PDF Report Export</t>
         </is>
       </c>
       <c r="C15" s="24">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A15, 'Module04'!$N$2:$N$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A15, 'Module04'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D15" s="25">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A15, 'Module04'!$N$2:$N$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A15, 'Module04'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E15" s="26">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A15, 'Module04'!$N$2:$N$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A15, 'Module04'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F15" s="27">
@@ -1196,24 +1190,24 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="28" t="inlineStr">
         <is>
-          <t>M04-F08</t>
+          <t>M04-SEC</t>
         </is>
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
-          <t>PDF Report Export</t>
+          <t>Access Control &amp; Security</t>
         </is>
       </c>
       <c r="C16" s="30">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A16, 'Module04'!$N$2:$N$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A16, 'Module04'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D16" s="31">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A16, 'Module04'!$N$2:$N$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A16, 'Module04'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E16" s="32">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A16, 'Module04'!$N$2:$N$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A16, 'Module04'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F16" s="33">
@@ -1224,24 +1218,24 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>M04-SEC</t>
+          <t>M04-F03</t>
         </is>
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>Access Control &amp; Security</t>
+          <t>Duplicate Record Prevention</t>
         </is>
       </c>
       <c r="C17" s="24">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A17, 'Module04'!$N$2:$N$24, "High")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A17, 'Module04'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D17" s="25">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A17, 'Module04'!$N$2:$N$24, "Medium")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A17, 'Module04'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E17" s="26">
-        <f>COUNTIFS('Module04'!$C$2:$C$24, A17, 'Module04'!$N$2:$N$24, "Low")</f>
+        <f>COUNTIFS('Module04'!$C$2:$C$34, A17, 'Module04'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F17" s="27">
@@ -1288,7 +1282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1444,10 +1438,14 @@
           <t>The record is saved successfully. A success message appears. The student's record is displayed in the list with all comments.</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>The record is saved successfully. A success message appears. The student's record is displayed in the list with all comments.</t>
+        </is>
+      </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
@@ -1518,10 +1516,14 @@
           <t>The record is saved successfully. No validation errors occur. No badges appear on the list for student ST002.</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>The record is saved successfully. No validation errors occur. No badges appear on the list for student ST002.</t>
+        </is>
+      </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr"/>
@@ -1590,10 +1592,14 @@
           <t>The record is saved successfully. The warning badge (⚠) appears next to the student's name in the list.</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>The record is saved successfully. The warning badge (⚠) appears next to the student's name in the list.</t>
+        </is>
+      </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
@@ -1662,10 +1668,14 @@
           <t>The record is saved successfully. No validation errors occur. The warning badge (⚠) is displayed on the student list.</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>The record is saved successfully. No validation errors occur. The warning badge (⚠) is displayed on the student list.</t>
+        </is>
+      </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr"/>
@@ -1680,7 +1690,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="75" customHeight="1">
+    <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC-M04-005</t>
@@ -1693,106 +1703,35 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>M04-F03</t>
+          <t>M04-F04</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Duplicate Record Prevention</t>
+          <t>Auto Draft Saving</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Block Duplicate Council Record for Same Student and Semester</t>
+          <t>Verify Automatic Draft Saving in Browser Local Storage</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Verify that the system blocks creating a second Class Council record for the same student in the same semester.</t>
+          <t>Verify that the system automatically saves typed comments into local storage in the background.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Staff user is logged in. A Class Council record already exists for ST001 in Semester 1.</t>
+          <t>Staff user is logged in. Bi-directional sync/save has not been initiated.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Student=ST001; Semester=Semester 1</t>
+          <t>Student=ST003; Semester=Semester 1; ITComment=Draft comment for IT department</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>1. Open Create Council Record;
-2. Select Student ST001 and Semester 'Semester 1';
-3. Enter any comment and click Save</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>The system rejects saving and displays error: 'Duplicate record error'. No duplicate record is created.</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>Related Requirement: M04-F03, One Record per Student per Semester 6.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>TC-M04-006</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Module 04</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>M04-F04</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Auto Draft Saving</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Verify Automatic Draft Saving in Browser Local Storage</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Verify that the system automatically saves typed comments into local storage in the background.</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Staff user is logged in. Bi-directional sync/save has not been initiated.</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>Student=ST003; Semester=Semester 1; ITComment=Draft comment for IT department</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>1. Open the council record for ST003 in Semester 1;
 2. Type IT Comment 'Draft comment for IT department';
@@ -1800,71 +1739,75 @@
 4. Open Developer Tools -&gt; Application -&gt; Local Storage</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>The text 'Draft comment for IT department' is saved automatically to browser Local Storage under a key representing ST003/Semester 1 as typing occurs.</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>The text 'Draft comment for IT department' is saved automatically to browser Local Storage under a key representing ST003/Semester 1 as typing occurs.</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F04, Automatic Draft Saving 6.5</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TC-M04-007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Module 04</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>M04-F05</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Draft Recovery / Discard</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Recover Unsaved Draft after Unexpected Browser Closure</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Verify that the system detects unsaved local drafts and displays a prompt to restore them.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Unsaved draft for ST003 with ITComment='Draft comment for IT department' exists in Local Storage. Sheets database does not have this comment.</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Student=ST003; Semester=Semester 1</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>1. Close browser and reopen it (simulating crash);
 2. Navigate back to the council record for ST003 in Semester 1;
@@ -1872,142 +1815,150 @@
 4. Select 'Continue editing'</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>An 'Unsaved Draft' warning/prompt is shown. Selecting 'Continue editing' restores the draft text 'Draft comment for IT department' to the IT Comment text box.</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="6" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>An 'Unsaved Draft' warning/prompt is shown. Selecting 'Continue editing' restores the draft text 'Draft comment for IT department' to the IT Comment text box.</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F05, Draft Recovery 6.6</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>TC-M04-008</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Module 04</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>M04-F05</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Draft Recovery / Discard</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Discard Unsaved Draft to Restore Last Saved Data</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Verify that choosing to discard an unsaved draft removes it and restores the last saved data from database.</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Official database record for ST003 has ITComment='Good student'. Unsaved draft in Local Storage has ITComment='Draft edit'.</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Student=ST003; Semester=Semester 1</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>1. Open council record for ST003 in Semester 1;
 2. When 'Unsaved Draft' prompt appears, select 'Discard draft';
 3. Check the IT Comment text box</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>Local Storage draft is cleared. The IT Comment reverts to the database value 'Good student'. Draft edits are discarded.</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Local Storage draft is cleared. The IT Comment reverts to the database value 'Good student'. Draft edits are discarded.</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O9" s="9" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F05, Draft Recovery 6.6</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="135" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TC-M04-009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="9" ht="135" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-008</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Module 04</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>M04-F06</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Batch Feedback Entry</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Batch Feedback Entry by Comment Type</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Verify that staff can enter the same feedback type for multiple students simultaneously in batch mode.</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Staff user is logged in. Students ST001, ST002, and ST003 exist in Batch PNV26A.</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Batch=PNV26A; Semester=Semester 1; FeedbackType=IT Comment; Comments='Active performance in programming project' for ST001, ST002, and ST003</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>1. Open Batch Feedback page;
 2. Select Batch PNV26A, Semester 'Semester 1', and Feedback Type 'IT Comment';
@@ -2015,71 +1966,75 @@
 4. Click Save All</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>All three records are saved successfully. Success message 'Saved 3 students' is shown. Selected students have the new IT comment.</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="6" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>All three records are saved successfully. Success message 'Saved 3 students' is shown. Selected students have the new IT comment.</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F06, Batch Feedback 6.7</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>TC-M04-010</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Module 04</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>M04-F06</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Batch Feedback Entry</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Batch Feedback Entry Does Not Overwrite Other Comment Fields</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Verify that entering batch feedback for one field does not erase other existing comment fields for that student.</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Student ST001 has existing ITComment='Excellent coding' and EnglishComment='Good speaking'.</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>FeedbackType=English Comment; NewEnglishComment='Excellent communication'</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>1. Open Batch Feedback page;
 2. Select Feedback Type 'English Comment';
@@ -2087,71 +2042,75 @@
 4. Navigate to ST001's council record details</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>English Comment is updated to 'Excellent communication'. The existing IT Comment is preserved as 'Excellent coding' (not cleared).</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>English Comment is updated to 'Excellent communication'. The existing IT Comment is preserved as 'Excellent coding' (not cleared).</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O11" s="9" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F06, Batch Feedback 6.7</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TC-M04-011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-010</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Module 04</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>M04-F07</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Concurrent Edit Conflict Handling</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Three-Way Merge for Non-conflicting Concurrent Edits</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Verify that concurrent edits on different fields of the same record are merged successfully using 3-way merge.</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Teacher A and Teacher B are logged in. The database record for ST001 has GeneralComment='Good student', other fields are empty.</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>ST001 record in Semester 1; Teacher B saves ITComment='Excellent'; Teacher A saves EnglishComment='Fluent'</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>1. Teacher A opens ST001 council edit form;
 2. Teacher B opens ST001 council edit form;
@@ -2159,71 +2118,75 @@
 4. Teacher A updates English Comment to 'Fluent' (IT Comment remains empty on their screen) and clicks Save</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>Save succeeds. The final record on Sheets is merged: GeneralComment='Good student', ITComment='Excellent', and EnglishComment='Fluent'. Teacher A receives notification of updates by another teacher.</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="6" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>Save succeeds. The final record on Sheets is merged: GeneralComment='Good student', ITComment='Excellent', and EnglishComment='Fluent'. Teacher A receives notification of updates by another teacher.</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F07, Concurrent Editing 6.8</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="135" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>TC-M04-012</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+    <row r="12" ht="135" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Module 04</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>M04-F07</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Concurrent Edit Conflict Handling</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Flag Conflict on Concurrent Edits of Same Field</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Verify that concurrent edits on the same field block the second user from overwriting first user's saved data and flag a conflict.</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Teacher A and Teacher B are logged in. ST001 has ITComment='Good'.</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>ST001 record in Semester 1; Teacher B saves ITComment='Excellent'; Teacher A saves ITComment='Very Good'</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>1. Teacher A opens ST001 edit form;
 2. Teacher B opens ST001 edit form;
@@ -2231,282 +2194,150 @@
 4. Teacher A changes IT Comment to 'Very Good' and clicks Save after Teacher B</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>Teacher A's save is blocked or triggers a conflict. An error 'Saved, but these fields were updated by another teacher: IT Comment' is shown. Teacher B's value 'Excellent' is preserved in database.</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr"/>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Teacher A's save is blocked or triggers a conflict. An error 'Saved, but these fields were updated by another teacher: IT Comment' is shown. Teacher B's value 'Excellent' is preserved in database.</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F07, Concurrent Editing 6.8</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="75" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TC-M04-013</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="13" ht="75" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-012</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Module 04</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>M04-F08</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>PDF Report Export</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Export Class Council Report to PDF</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Verify that staff can generate and download a PDF report containing student info, semester, comments, and warnings.</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>Student ST001 has a complete council record in Semester 1.</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>Student=ST001; Semester=Semester 1</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>1. Open ST001's council record details page;
 2. Click Export PDF;
 3. Open the downloaded PDF file</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>The PDF report downloads successfully. It contains student details, Semester 1, all teacher comments, and warning details formatted correctly.</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="6" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>The PDF report downloads successfully. It contains student details, Semester 1, all teacher comments, and warning details formatted correctly.</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="O13" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M04-F08, PDF Export 6.9</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>TC-M04-014</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Module 04</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>M04-F01</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Council Feedback Record</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Trend Chart Hidden for Semester 1</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Verify that the trend chart is hidden on the report when viewing/exporting Semester 1 results.</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Student ST001 has a council record in Semester 1.</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>Student=ST001; Semester=Semester 1</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>1. Open or export PDF report for ST001 in Semester 1;
-2. Check the Trend Chart section</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>No trend chart is displayed on the UI or PDF report for Semester 1 (since no prior semester history exists).</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="O15" s="9" t="inlineStr">
-        <is>
-          <t>Related Requirement: Business Rules, Trend Chart 6.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TC-M04-015</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Module 04</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>M04-F01</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Council Feedback Record</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Trend Chart Displayed for Semester 2 or Later</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Verify that the trend chart is shown when viewing/exporting results for Semester 2 or later.</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Student ST001 has council records and grade history in both Semester 1 and Semester 2.</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Student=ST001; Semester=Semester 2</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>1. Open or export PDF report for ST001 in Semester 2;
-2. Check the Trend Chart section</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>The trend chart is displayed successfully in the UI and PDF, depicting ST001's performance trend from Semester 1 to Semester 2.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>Related Requirement: Business Rules, Trend Chart 6.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="120" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>TC-M04-016</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Module 04</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>M04-F02</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Academic Warning Flag</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Badge Display Activation on Content Entry</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Verify that saving comments activates their corresponding badges (G, IT, EN, PLT, ED) on the student list.</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. ST001 has no comments in Semester 1.</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Student=ST001; Semester=Semester 1; ITComment='Good'; EducatorComment='Active'</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>1. Create council record for ST001 in Semester 1;
 2. Input IT Comment 'Good' and Educator Comment 'Active' (others left empty);
@@ -2514,71 +2345,75 @@
 4. Go to student list and observe ST001 row</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Only 'IT' and 'ED' badges are activated/displayed next to ST001's name. Other badges (G, EN, PLT, ⚠) are hidden.</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="10" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Only 'IT' and 'ED' badges are activated/displayed next to ST001's name. Other badges (G, EN, PLT, ⚠) are hidden.</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="O17" s="9" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: Business Rules, Badge Display 6.4</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="105" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TC-M04-017</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+    <row r="15" ht="105" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-014</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Module 04</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>M04-F02</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Academic Warning Flag</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Badge Display Deactivation on Content Removal</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>Verify that removing comment content deactivates the corresponding badge on save.</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Student ST001 has an IT comment and the 'IT' badge is active.</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Student=ST001; Semester=Semester 1; ITComment=''</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>1. Open ST001's Semester 1 council record;
 2. Clear the IT Comment field completely;
@@ -2586,464 +2421,1482 @@
 4. Go to student list and observe badges</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>The record is updated. The 'IT' badge disappears from ST001's name on the list since its comment was removed.</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="10" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>The record is updated. The 'IT' badge disappears from ST001's name on the list since its comment was removed.</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: Business Rules, Badge Display 6.4</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="105" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>TC-M04-018</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Module 04</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>M04-F01</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Council Feedback Record</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>Record Saving Fails with Missing Student Selection</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Verify that the system blocks saving if the student selection is missing.</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>Staff user is logged in.</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>Student=Empty; Semester=Semester 1; GeneralComment=Good</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>1. Navigate to Create Council Record;
-2. Leave Student selection empty;
-3. Select Semester 'Semester 1';
-4. Enter General Comment 'Good' and click Save</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>Saving is blocked. Validation error message requires student selection. The student field is highlighted in red.</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O19" s="9" t="inlineStr">
-        <is>
-          <t>Related Requirement: Validation Rules 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="105" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TC-M04-019</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Module 04</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>M04-F01</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Council Feedback Record</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Record Saving Fails with Missing Semester Selection</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Verify that the system blocks saving if the semester selection is missing.</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Staff user is logged in.</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Student=ST001; Semester=Empty; GeneralComment=Good</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>1. Navigate to Create Council Record;
-2. Select Student ST001;
-3. Leave Semester selection empty;
-4. Enter General Comment 'Good' and click Save</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>Saving is blocked. Validation error message requires semester selection. The semester field is highlighted in red.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>Related Requirement: Validation Rules 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="75" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>TC-M04-020</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Module 04</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>M04-SEC</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Access Control &amp; Security</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Block Student Access to Class Council Management</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>Verify that a user logged in with a Student email domain cannot access Class Council Management.</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>User logged in with student email student01@student.passerellesnumeriques.org.</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>Email=student01@student.passerellesnumeriques.org</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>1. Log in with student account;
-2. Attempt direct URL navigation to Class Council Management page;
-3. Observe UI</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>Access is denied. An 'Access Denied' message is shown, or user is redirected to student home page. Management menu is hidden.</t>
-        </is>
-      </c>
-      <c r="K21" s="9" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O21" s="9" t="inlineStr">
-        <is>
-          <t>Related Requirement: General Rules, User Roles</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TC-M04-021</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Module 04</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>M04-SEC</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Access Control &amp; Security</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Block Unknown Email Domain Access</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Verify that users with unauthorized email domains (non-PNV/non-student) are completely blocked.</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>User is authenticated with email testuser@gmail.com.</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Email=testuser@gmail.com</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>1. Enter application URL;
 2. Sign in via Google OAuth with testuser@gmail.com</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Login fails or 'Access Denied' message displays. User is blocked from accessing any management features.</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="6" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Login fails or 'Access Denied' message displays. User is blocked from accessing any management features.</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: General Rules, User Roles</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="135" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>TC-M04-022</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+    <row r="17" ht="135" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-016</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Module 04</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>M04-F04</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Auto Draft Saving</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Verify Draft Storage Device Specificity</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Verify that local drafts are device-specific and not synchronized to other computers.</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Staff user logged in on Computer X and Computer Y.</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>Computer X: input IT Comment 'Draft text on Computer X' for ST003.</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>1. On Computer X, open ST003 council form and type IT comment 'Draft text on Computer X' (wait for auto-save, do NOT click Save);
 2. On Computer Y, log in to same account and open ST003 Semester 1 council form;
 3. Verify if draft warning appears</t>
         </is>
       </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>No 'Unsaved Draft' warning appears on Computer Y, and the IT comment field is empty (or displays the saved Sheets value). Draft is device-specific.</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>No 'Unsaved Draft' warning appears on Computer Y, and the IT comment field is empty (or displays the saved Sheets value). Draft is device-specific.</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F04, Automatic Draft Saving 6.5, Out of Scope 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="135" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>M04-F03</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Duplicate Record Prevention</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Prevent Duplicate Council Record Creation</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Verify that the system blocks creating a second Class Council record for a student in the same semester.</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. A Class Council record already exists for ST001 in Semester 1.</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>1. Navigate to Class Council Management;
+2. Click Create Council Record;
+3. Select Student ST001 and Semester 'Semester 1';
+4. Enter General Comment 'Second record test';
+5. Click Save</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: 'A council record already exists for this student in Semester 1.' Duplicate record is blocked.</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: 'A council record already exists for this student in Semester 1.' Duplicate record is blocked.</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F03, Business Rule 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="135" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-018</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>M04-F03</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Duplicate Record Prevention</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Allow Council Record in Different Semester</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Verify that the system allows creating a council record for a student in Semester 2 even if a record exists in Semester 1.</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Council record exists for ST001 in Semester 1. No record exists for ST001 in Semester 2.</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 2; GeneralComment=Progressing well in term 2</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>1. Navigate to Class Council Management;
+2. Click Create Council Record;
+3. Select Student ST001 and Semester 'Semester 2';
+4. Enter General Comment 'Progressing well in term 2';
+5. Click Save</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>The record for Semester 2 is saved successfully. ST001 now has two distinct records for Semester 1 and Semester 2.</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>The record for Semester 2 is saved successfully. ST001 now has two distinct records for Semester 1 and Semester 2.</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F03, Business Rule 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>M04-F08</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>PDF Report Export</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Hide Trend Chart in Semester 1 PDF Export</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Verify that trend charts are not displayed in PDF exports for Semester 1 records due to lack of historical data.</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Council record for ST001 in Semester 1 exists.</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST001 in Semester 1;
+2. Click Export PDF;
+3. Open and inspect the downloaded PDF report</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>PDF report generates successfully. Student details and comments are present. Trend chart section is omitted/not displayed for Semester 1.</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>PDF report generates successfully. Student details and comments are present. Trend chart section is omitted/not displayed for Semester 1.</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F08, Business Rule 6.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="75" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-020</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>M04-F08</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>PDF Report Export</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Display Trend Chart in Semester 2 PDF Export</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Verify that trend charts are automatically generated and displayed in PDF exports for Semester 2 when historical data exists.</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Council records exist for ST001 in both Semester 1 and Semester 2.</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 2</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST001 in Semester 2;
+2. Click Export PDF;
+3. Open and inspect the downloaded PDF report</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>PDF report generates successfully. Evaluation trend chart comparing Semester 1 and Semester 2 is displayed in the report.</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>PDF report generates successfully. Evaluation trend chart comparing Semester 1 and Semester 2 is displayed in the report.</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F08, Business Rule 6.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="135" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>M04-F02</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Academic Warning Flag</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Deactivate Academic Warning Flag and Clear Reason</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Verify that unchecking the Academic Warning flag removes the warning badge and clears the warning reason upon saving.</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Student ST001 has an active academic warning with reason 'Attendance below required level'.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1; Warning=False; WarningReason=''</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST001 in Semester 1;
+2. Uncheck the 'Academic Warning' checkbox;
+3. Clear the Warning Reason text box;
+4. Click Save;
+5. Observe student list row for ST001</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Record updates successfully. Warning badge (⚠) is removed from ST001 in the list view. Warning reason is cleared.</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Record updates successfully. Warning badge (⚠) is removed from ST001 in the list view. Warning reason is cleared.</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F02, Business Rule 6.3, 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-022</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>M04-F01</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Council Feedback Record</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Update Existing Class Council Evaluation Comments</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Verify that staff can open an existing council record and update feedback comments from multiple departments.</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Record for ST001 in Semester 1 exists with initial IT Comment 'Good'.</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1; ITComment=Outstanding programming progress; EnglishComment=Improved presentation skills</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>1. Navigate to Class Council Management;
+2. Open edit form for ST001 Semester 1 record;
+3. Update IT Comment to 'Outstanding programming progress';
+4. Update English Comment to 'Improved presentation skills';
+5. Click Save</t>
+        </is>
+      </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>No 'Unsaved Draft' warning appears on Computer Y, and the IT comment field is empty (or displays the saved Sheets value). Draft is device-specific.</t>
-        </is>
-      </c>
-      <c r="K23" s="9" t="inlineStr"/>
+          <t>Record updates successfully. New comments are persisted. Badges 'IT' and 'EN' remain active on the student list.</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>Record updates successfully. New comments are persisted. Badges 'IT' and 'EN' remain active on the student list.</t>
+        </is>
+      </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="10" t="inlineStr">
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="120" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>M04-F01</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Council Feedback Record</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Block Saving Council Record Without Student</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Verify that the system enforces student selection as a required field when creating a council record.</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Staff user is logged in.</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Student=Unselected; Semester=Semester 1; GeneralComment=Test comment</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>1. Open Create Council Record form;
+2. Leave Student unselected;
+3. Select Semester 'Semester 1';
+4. Enter General Comment 'Test comment';
+5. Click Save</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Form submission is blocked. Validation error message appears: 'Student is required.' Record is not saved.</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Form submission is blocked. Validation error message appears: 'Student is required.' Record is not saved.</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>Related Requirement: Validation Rules 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-024</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>M04-F01</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Council Feedback Record</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Block Saving Council Record Without Semester</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Verify that the system enforces semester selection as a required field when creating a council record.</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Student ST001 exists.</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Unselected; GeneralComment=Test comment</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>1. Open Create Council Record form;
+2. Select Student ST001;
+3. Leave Semester unselected;
+4. Enter General Comment 'Test comment';
+5. Click Save</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>Form submission is blocked. Validation error message appears: 'Semester is required.' Record is not saved.</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Form submission is blocked. Validation error message appears: 'Semester is required.' Record is not saved.</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="inlineStr">
+        <is>
+          <t>Related Requirement: Validation Rules 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="120" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>M04-F06</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Batch Feedback Entry</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Clear Comment Field Across Multiple Students via Batch Entry</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Students ST001 and ST002 have existing PLT comments.</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Batch=PNV26A; Semester=Semester 1; FeedbackType=PLT Comment; Comments='' for ST001 and ST002</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>1. Open Batch Feedback page;
+2. Select Batch PNV26A, Semester 'Semester 1', and Feedback Type 'PLT Comment';
+3. Clear comments for ST001 and ST002 in the grid;
+4. Click Save All</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Batch update succeeds. PLT comments for ST001 and ST002 are removed</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>and 'PLT' badge is deactivated for both students.</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>and 'PLT' badge is deactivated for both students.</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="O23" s="9" t="inlineStr">
-        <is>
-          <t>Related Requirement: M04-F04, Automatic Draft Saving 6.5, Out of Scope 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="105" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TC-M04-023</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F06, Business Rule 6.4, 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="120" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-026</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Module 04</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>M04-F06</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Batch Feedback Entry</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Batch Feedback Entry with Empty Student List</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Verify that batch feedback entry behaves gracefully when the selected batch has no active students.</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Batch PNV26B is active but has no active students.</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Batch=PNV26B; Semester=Semester 1; FeedbackType=IT Comment</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Save Batch Feedback Without Modifying Any Comments</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Verify system behavior when clicking Save All in batch mode without modifying any student comments.</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Batch PNV26A has 5 active students.</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Batch=PNV26A; Semester=Semester 1; FeedbackType=General Comment; No edits made</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>1. Open Batch Feedback page;
-2. Select Batch PNV26B, Semester 'Semester 1', and Feedback Type 'IT Comment';
-3. Verify student list;
+2. Select Batch PNV26A, Semester 'Semester 1', and Feedback Type 'General Comment';
+3. Do NOT edit any comment cells;
 4. Click Save All</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>The student grid is empty or shows 'No students in this batch'. Clicking Save All shows 'Saved 0 students' successfully with no crashes or errors.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="10" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>System notifies 'No changes to save' or successfully processes 0 updates without errors. Existing data remains unchanged.</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>System notifies 'No changes to save' or successfully processes 0 updates without errors. Existing data remains unchanged.</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O27" s="9" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F06</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="105" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>M04-F07</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Concurrent Edit Conflict Handling</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Handle Concurrent Edits When Both Users Enter Identical Text</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Verify that when two teachers edit the same comment field with identical text</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Teacher A and Teacher B are logged in. ST001 has GeneralComment='Initial state'.</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>ST001 record in Semester 1; Teacher B saves ITComment='Excellent'; Teacher A saves ITComment='Excellent'</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>1. Teacher A and Teacher B open ST001 edit form concurrently;
+2. Teacher B enters IT Comment 'Excellent' and saves first;
+3. Teacher A enters identical IT Comment 'Excellent' and saves second</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Save succeeds smoothly without error. The field value remains 'Excellent'.</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Save succeeds smoothly without error. The field value remains 'Excellent'.</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>Related Requirement: M04-F06</t>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F07, Concurrent Editing 6.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="120" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-028</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>M04-F04</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Auto Draft Saving</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Clear Local Storage Draft After Successful Official Record Save</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Verify that saving an official record successfully purges the local storage draft key for that record.</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Typing in progress for ST001</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1; ITComment=Finalized comment</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST001 and type IT Comment 'Finalized comment';
+2. Verify draft exists in Local Storage;
+3. Click Save button;
+4. Open Developer Tools -&gt; Application -&gt; Local Storage</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>Record is saved to database. Local Storage draft entry for ST001/Semester 1 is completely deleted upon successful save.</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>Record is saved to database. Local Storage draft entry for ST001/Semester 1 is completely deleted upon successful save.</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F04, M04-F05, Business Rule 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="105" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>M04-SEC</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Access Control &amp; Security</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Block Student Account From Accessing Council Edit Forms</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Verify that student user accounts cannot access Class Council edit pages or perform save actions.</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>User is authenticated with a valid Student account.</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>UserRole=Student; TargetURL=/class-council/edit/ST001</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>1. Log in with student account;
+2. Attempt to directly navigate to Class Council Edit URL (/class-council/edit/ST001);
+3. Attempt to invoke council record save API</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Access is denied. Page redirects to dashboard or displays '403 Forbidden / Access Denied'. API request is rejected.</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Access is denied. Page redirects to dashboard or displays '403 Forbidden / Access Denied'. API request is rejected.</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>Related Requirement: General Rules, User Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="120" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-030</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>M04-F08</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>PDF Report Export</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Export Batch Class Council Reports to Combined Package</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Verify that staff can select a batch and export all student council reports for a semester in one click.</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Batch PNV26A has 5 students with saved council records in Semester 1.</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>Batch=PNV26A; Semester=Semester 1; ExportType=Batch PDF</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>1. Open Class Council Overview;
+2. Filter by Batch PNV26A and Semester 'Semester 1';
+3. Click 'Export Batch Reports (PDF)';
+4. Download and extract/open exported file</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>Combined archive or PDF containing reports for all 5 students downloads successfully. All reports are complete and accurate.</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>Combined archive or PDF containing reports for all 5 students downloads successfully. All reports are complete and accurate.</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F08, PDF Export 6.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="120" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>M04-F05</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Draft Recovery / Discard</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Discard Draft Changes Manually via Form Action Button</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Verify that staff can discard active local draft edits at any time using the 'Discard Draft' button on the form.</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Council record for ST001 has saved ITComment='Saved IT Comment'. Local draft has ITComment='Unsaved edit'.</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST001;
+2. Observe unsaved draft text 'Unsaved edit' in IT Comment field;
+3. Click 'Discard Draft' button in form header;
+4. Confirm discard action in modal prompt</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Unsaved local draft is discarded. IT Comment field immediately reverts to 'Saved IT Comment'. Local storage key is cleared.</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Unsaved local draft is discarded. IT Comment field immediately reverts to 'Saved IT Comment'. Local storage key is cleared.</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F05, Business Rule 6.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="120" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>TC-M04-032</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>M04-F04</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Auto Draft Saving</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Retain Draft Comments in Local Storage During Network Disconnection</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Verify that local draft auto-saving continues working seamlessly when user loses internet connection.</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Staff user is logged in and editing council record for ST002.</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>Student=ST002; Semester=Semester 1; ITComment=Offline draft comment</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST002;
+2. Disconnect internet network connection;
+3. Type IT Comment 'Offline draft comment';
+4. Observe local storage and UI offline indicator</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>System indicates offline status. Comment text 'Offline draft comment' is safely stored in browser Local Storage without data loss.</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>System indicates offline status. Comment text 'Offline draft comment' is safely stored in browser Local Storage without data loss.</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F04, Business Rule 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="75" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TC-M04-033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>M04-F08</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>PDF Report Export</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Export PDF Report for Council Record with Partial Comments</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Verify that exporting a PDF report works properly even if some optional department comments are left blank.</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. ST002 has a saved council record with only IT Comment filled (others empty).</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Student=ST002; Semester=Semester 1</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST002 in Semester 1;
+2. Click Export PDF;
+3. Download and inspect PDF report</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>PDF report exports successfully without errors. Blank comment sections display 'N/A' or remain neatly empty without breaking PDF layout.</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>PDF report exports successfully without errors. Blank comment sections display 'N/A' or remain neatly empty without breaking PDF layout.</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F08, Business Rule 6.2, 6.9</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O24"/>
+  <autoFilter ref="A1:O34"/>
   <dataValidations count="2">
-    <dataValidation sqref="L2:L124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
+    <dataValidation sqref="L2:L134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
       <formula1>"Passed,Failed,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
+    <dataValidation sqref="N2:N134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
